--- a/AAII_Financials/Yearly/RAASY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RAASY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>RAASY</t>
   </si>
@@ -1683,7 +1683,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>81700</v>
+        <v>83500</v>
       </c>
       <c r="E42" s="3">
         <v>72100</v>
@@ -1716,7 +1716,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>28200</v>
+        <v>28400</v>
       </c>
       <c r="E43" s="3">
         <v>20400</v>
@@ -1748,8 +1748,8 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>500</v>
       </c>
       <c r="E44" s="3">
         <v>400</v>
@@ -1782,7 +1782,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>16500</v>
+        <v>14000</v>
       </c>
       <c r="E45" s="3">
         <v>14700</v>
@@ -2208,7 +2208,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>42800</v>
+        <v>48200</v>
       </c>
       <c r="E59" s="3">
         <v>49300</v>
@@ -2903,7 +2903,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
         <v>1800</v>
